--- a/myapp/src/main/resources/plantilla4.xlsx
+++ b/myapp/src/main/resources/plantilla4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1552A4A-1E95-40CE-A834-B4475C083F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26754E14-A8DE-45FA-AA99-A55A974FC3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="2820" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5475" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado" sheetId="1" r:id="rId1"/>
@@ -217,13 +217,13 @@
     <t>Guarico</t>
   </si>
   <si>
-    <t>TS260001050</t>
-  </si>
-  <si>
     <t>Placas solares</t>
   </si>
   <si>
     <t>LISTADO MATERIALES OL</t>
+  </si>
+  <si>
+    <t>OT260001050</t>
   </si>
 </sst>
 </file>
@@ -583,6 +583,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,8 +612,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,14 +938,14 @@
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
+      <c r="D2" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="8"/>
       <c r="M2" s="25"/>
     </row>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="6"/>
@@ -999,14 +999,14 @@
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="42"/>
-      <c r="L5" s="37" t="s">
+      <c r="K5" s="44"/>
+      <c r="L5" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="38"/>
+      <c r="M5" s="40"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -1016,22 +1016,22 @@
       <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="41"/>
+      <c r="D6" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="43"/>
       <c r="F6" s="6"/>
       <c r="G6" s="27"/>
       <c r="H6" s="27"/>
       <c r="I6" s="33"/>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="43"/>
-      <c r="L6" s="39">
+      <c r="K6" s="45"/>
+      <c r="L6" s="41">
         <v>46065</v>
       </c>
-      <c r="M6" s="40"/>
+      <c r="M6" s="42"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
@@ -1043,14 +1043,14 @@
       <c r="G7" s="28"/>
       <c r="H7" s="28"/>
       <c r="I7" s="33"/>
-      <c r="J7" s="44" t="s">
+      <c r="J7" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="39">
+      <c r="K7" s="46"/>
+      <c r="L7" s="41">
         <v>46072</v>
       </c>
-      <c r="M7" s="40"/>
+      <c r="M7" s="42"/>
     </row>
     <row r="8" spans="1:15" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
@@ -1084,14 +1084,14 @@
       <c r="E9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
@@ -1109,14 +1109,14 @@
       <c r="E10" s="21">
         <v>1</v>
       </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
@@ -1134,15 +1134,15 @@
       <c r="E11" s="21">
         <v>1</v>
       </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="O11" s="46"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="O11" s="37"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
@@ -1160,14 +1160,14 @@
       <c r="E12" s="21">
         <v>1</v>
       </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
@@ -1185,14 +1185,14 @@
       <c r="E13" s="21">
         <v>4</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
@@ -1210,14 +1210,14 @@
       <c r="E14" s="21">
         <v>1</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="19"/>
@@ -1233,14 +1233,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
@@ -1258,14 +1258,14 @@
       <c r="E16" s="21">
         <v>4</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
@@ -1283,14 +1283,14 @@
       <c r="E17" s="21">
         <v>4</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
@@ -1308,14 +1308,14 @@
       <c r="E18" s="21">
         <v>3</v>
       </c>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
@@ -1333,14 +1333,14 @@
       <c r="E19" s="21">
         <v>1</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
@@ -1358,14 +1358,14 @@
       <c r="E20" s="21">
         <v>1</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
@@ -1383,14 +1383,14 @@
       <c r="E21" s="21">
         <v>1</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
@@ -1408,14 +1408,14 @@
       <c r="E22" s="21">
         <v>1</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
@@ -1433,14 +1433,14 @@
       <c r="E23" s="21">
         <v>2</v>
       </c>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
@@ -1458,14 +1458,14 @@
       <c r="E24" s="21">
         <v>1</v>
       </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
@@ -1483,14 +1483,14 @@
       <c r="E25" s="21">
         <v>1</v>
       </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
@@ -1508,14 +1508,14 @@
       <c r="E26" s="21">
         <v>2</v>
       </c>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
@@ -1533,14 +1533,14 @@
       <c r="E27" s="21">
         <v>1</v>
       </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
@@ -1558,14 +1558,14 @@
       <c r="E28" s="21">
         <v>2</v>
       </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
@@ -1583,14 +1583,14 @@
       <c r="E29" s="21">
         <v>2</v>
       </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
@@ -1608,14 +1608,14 @@
       <c r="E30" s="21">
         <v>1</v>
       </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
@@ -1633,14 +1633,14 @@
       <c r="E31" s="21">
         <v>2</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
@@ -1658,14 +1658,14 @@
       <c r="E32" s="21">
         <v>1</v>
       </c>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
@@ -1683,14 +1683,14 @@
       <c r="E33" s="21">
         <v>2</v>
       </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
@@ -1708,14 +1708,14 @@
       <c r="E34" s="21">
         <v>4</v>
       </c>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
@@ -1733,14 +1733,14 @@
       <c r="E35" s="21">
         <v>3</v>
       </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
@@ -1758,14 +1758,14 @@
       <c r="E36" s="21">
         <v>1</v>
       </c>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
@@ -1783,14 +1783,14 @@
       <c r="E37" s="21">
         <v>1</v>
       </c>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
@@ -1808,14 +1808,14 @@
       <c r="E38" s="21">
         <v>1</v>
       </c>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
@@ -1833,14 +1833,14 @@
       <c r="E39" s="21">
         <v>4</v>
       </c>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
@@ -1858,14 +1858,14 @@
       <c r="E40" s="21">
         <v>2</v>
       </c>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
@@ -1883,14 +1883,14 @@
       <c r="E41" s="21">
         <v>4</v>
       </c>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
@@ -1908,14 +1908,14 @@
       <c r="E42" s="21">
         <v>1</v>
       </c>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
@@ -1933,14 +1933,14 @@
       <c r="E43" s="21">
         <v>2</v>
       </c>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
@@ -1958,14 +1958,14 @@
       <c r="E44" s="21">
         <v>1</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="19">
@@ -1983,14 +1983,14 @@
       <c r="E45" s="21">
         <v>1</v>
       </c>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
-      <c r="M45" s="45"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="19">
@@ -2008,14 +2008,14 @@
       <c r="E46" s="21">
         <v>1</v>
       </c>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="45"/>
-      <c r="M46" s="45"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="19">
@@ -2033,14 +2033,14 @@
       <c r="E47" s="21">
         <v>2</v>
       </c>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="45"/>
-      <c r="M47" s="45"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
@@ -2058,14 +2058,14 @@
       <c r="E48" s="21">
         <v>1</v>
       </c>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-      <c r="M48" s="45"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="19">
@@ -2083,14 +2083,14 @@
       <c r="E49" s="21">
         <v>4</v>
       </c>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="45"/>
-      <c r="M49" s="45"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
@@ -2108,14 +2108,14 @@
       <c r="E50" s="21">
         <v>4</v>
       </c>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="19">
@@ -2133,14 +2133,14 @@
       <c r="E51" s="21">
         <v>1</v>
       </c>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="45"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="36"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
@@ -2158,14 +2158,14 @@
       <c r="E52" s="21">
         <v>1</v>
       </c>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="45"/>
-      <c r="M52" s="45"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="36"/>
+      <c r="L52" s="36"/>
+      <c r="M52" s="36"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="19"/>
@@ -2181,14 +2181,14 @@
       <c r="E53" s="21">
         <v>1</v>
       </c>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
@@ -2206,14 +2206,14 @@
       <c r="E54" s="21">
         <v>1</v>
       </c>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="45"/>
-      <c r="M54" s="45"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="19">
@@ -2231,14 +2231,14 @@
       <c r="E55" s="21">
         <v>1</v>
       </c>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="45"/>
-      <c r="M55" s="45"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="36"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
@@ -2256,14 +2256,14 @@
       <c r="E56" s="21">
         <v>1</v>
       </c>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="45"/>
-      <c r="M56" s="45"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="19">
@@ -2281,14 +2281,14 @@
       <c r="E57" s="21">
         <v>1</v>
       </c>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
-      <c r="L57" s="45"/>
-      <c r="M57" s="45"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="36"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
@@ -2306,14 +2306,14 @@
       <c r="E58" s="21">
         <v>1</v>
       </c>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="45"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
+      <c r="L58" s="36"/>
+      <c r="M58" s="36"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="19">
@@ -2331,14 +2331,14 @@
       <c r="E59" s="21">
         <v>1</v>
       </c>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
-      <c r="L59" s="45"/>
-      <c r="M59" s="45"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="19">
@@ -2356,14 +2356,14 @@
       <c r="E60" s="21">
         <v>1</v>
       </c>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="45"/>
-      <c r="M60" s="45"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="36"/>
+      <c r="K60" s="36"/>
+      <c r="L60" s="36"/>
+      <c r="M60" s="36"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="19">
@@ -2381,14 +2381,14 @@
       <c r="E61" s="21">
         <v>2</v>
       </c>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
-      <c r="L61" s="45"/>
-      <c r="M61" s="45"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="36"/>
+      <c r="K61" s="36"/>
+      <c r="L61" s="36"/>
+      <c r="M61" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="8">
